--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/197.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/197.xlsx
@@ -426,13 +426,13 @@
         <v>-1.199532264075858</v>
       </c>
       <c r="E2">
-        <v>-16.25817021531179</v>
+        <v>-16.74675633294736</v>
       </c>
       <c r="F2">
-        <v>-2.978387688706505</v>
+        <v>-3.724422826974365</v>
       </c>
       <c r="G2">
-        <v>-10.07291860991583</v>
+        <v>-8.90272021487641</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.305151651528244</v>
       </c>
       <c r="E3">
-        <v>-17.74294815905072</v>
+        <v>-17.07363064376902</v>
       </c>
       <c r="F3">
-        <v>-2.674685832920331</v>
+        <v>-4.194966161358388</v>
       </c>
       <c r="G3">
-        <v>-9.187473478891283</v>
+        <v>-9.036714545578411</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.426052353486578</v>
       </c>
       <c r="E4">
-        <v>-18.66557945337347</v>
+        <v>-17.06619488944843</v>
       </c>
       <c r="F4">
-        <v>-3.111348940529854</v>
+        <v>-3.764390725792038</v>
       </c>
       <c r="G4">
-        <v>-9.853518825391713</v>
+        <v>-8.613600341295239</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.545728934008175</v>
       </c>
       <c r="E5">
-        <v>-18.68637420601669</v>
+        <v>-18.46276721646595</v>
       </c>
       <c r="F5">
-        <v>-3.132285098268208</v>
+        <v>-3.805811581034222</v>
       </c>
       <c r="G5">
-        <v>-9.944148320074801</v>
+        <v>-8.847910822928236</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.659052889328807</v>
       </c>
       <c r="E6">
-        <v>-18.31098635315086</v>
+        <v>-20.20452247471814</v>
       </c>
       <c r="F6">
-        <v>-3.707818202385249</v>
+        <v>-3.690029012410129</v>
       </c>
       <c r="G6">
-        <v>-9.815232366230042</v>
+        <v>-8.198524141581418</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.753302143176415</v>
       </c>
       <c r="E7">
-        <v>-19.62445665365362</v>
+        <v>-19.54158105083925</v>
       </c>
       <c r="F7">
-        <v>-3.108370131349387</v>
+        <v>-3.698442740120364</v>
       </c>
       <c r="G7">
-        <v>-9.775608446670505</v>
+        <v>-8.338791956080339</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.819311488696365</v>
       </c>
       <c r="E8">
-        <v>-21.39465072867399</v>
+        <v>-19.12828987052922</v>
       </c>
       <c r="F8">
-        <v>-3.167088126329427</v>
+        <v>-3.870235370684745</v>
       </c>
       <c r="G8">
-        <v>-9.810458559562413</v>
+        <v>-8.281251364062266</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.845664618357186</v>
       </c>
       <c r="E9">
-        <v>-21.14825192944264</v>
+        <v>-20.75448300057967</v>
       </c>
       <c r="F9">
-        <v>-3.318006726710663</v>
+        <v>-3.696162244660457</v>
       </c>
       <c r="G9">
-        <v>-8.977568338973793</v>
+        <v>-8.341089474684592</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.822848157131983</v>
       </c>
       <c r="E10">
-        <v>-21.80815021878838</v>
+        <v>-20.72584493095516</v>
       </c>
       <c r="F10">
-        <v>-3.016203489011705</v>
+        <v>-3.755613344791975</v>
       </c>
       <c r="G10">
-        <v>-9.173238133072417</v>
+        <v>-6.917697246256171</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.744539963321632</v>
       </c>
       <c r="E11">
-        <v>-22.47053011189032</v>
+        <v>-21.57127027192115</v>
       </c>
       <c r="F11">
-        <v>-3.023932985247227</v>
+        <v>-3.96551004751773</v>
       </c>
       <c r="G11">
-        <v>-8.241346048131891</v>
+        <v>-7.49758233455153</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.608973053904316</v>
       </c>
       <c r="E12">
-        <v>-21.14590617990667</v>
+        <v>-22.76338199749236</v>
       </c>
       <c r="F12">
-        <v>-3.754929113317262</v>
+        <v>-3.740078970887275</v>
       </c>
       <c r="G12">
-        <v>-7.536289232996689</v>
+        <v>-7.458100768450182</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.419157688015472</v>
       </c>
       <c r="E13">
-        <v>-24.22565795388717</v>
+        <v>-22.6720155059136</v>
       </c>
       <c r="F13">
-        <v>-2.831043493668349</v>
+        <v>-3.69755970046898</v>
       </c>
       <c r="G13">
-        <v>-7.262318415803223</v>
+        <v>-6.50198211125327</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.182153206515865</v>
       </c>
       <c r="E14">
-        <v>-22.64250344080561</v>
+        <v>-22.27010890925885</v>
       </c>
       <c r="F14">
-        <v>-3.171578706020003</v>
+        <v>-3.177892522364141</v>
       </c>
       <c r="G14">
-        <v>-6.670240588286728</v>
+        <v>-6.508434364509309</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.9059780829758084</v>
       </c>
       <c r="E15">
-        <v>-26.75809835930063</v>
+        <v>-23.57394261707329</v>
       </c>
       <c r="F15">
-        <v>-2.718989406724257</v>
+        <v>-3.284513347513271</v>
       </c>
       <c r="G15">
-        <v>-6.665761420172094</v>
+        <v>-5.5633000974117</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.598058747779687</v>
       </c>
       <c r="E16">
-        <v>-24.1329872617942</v>
+        <v>-25.19477856237267</v>
       </c>
       <c r="F16">
-        <v>-2.603192755854316</v>
+        <v>-3.196126545634563</v>
       </c>
       <c r="G16">
-        <v>-6.279248607371104</v>
+        <v>-5.194296759967916</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.2651517850124663</v>
       </c>
       <c r="E17">
-        <v>-26.54305471409839</v>
+        <v>-25.59668968750143</v>
       </c>
       <c r="F17">
-        <v>-2.753114830249985</v>
+        <v>-3.442813529820854</v>
       </c>
       <c r="G17">
-        <v>-6.293907703018998</v>
+        <v>-5.060842048188816</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.08539437964626319</v>
       </c>
       <c r="E18">
-        <v>-27.49413841061134</v>
+        <v>-26.22801783433278</v>
       </c>
       <c r="F18">
-        <v>-2.030636804182937</v>
+        <v>-3.313310711904193</v>
       </c>
       <c r="G18">
-        <v>-6.297787662391023</v>
+        <v>-5.13318077876743</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.445720320969377</v>
       </c>
       <c r="E19">
-        <v>-27.72465132302379</v>
+        <v>-27.27585237801961</v>
       </c>
       <c r="F19">
-        <v>-2.685110836684562</v>
+        <v>-2.811351543768999</v>
       </c>
       <c r="G19">
-        <v>-6.016315149005569</v>
+        <v>-5.26245758207597</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.80588038772728</v>
       </c>
       <c r="E20">
-        <v>-27.32029935040489</v>
+        <v>-27.2038813406157</v>
       </c>
       <c r="F20">
-        <v>-2.01245165458928</v>
+        <v>-2.40212230780539</v>
       </c>
       <c r="G20">
-        <v>-5.335090951207579</v>
+        <v>-4.158599209098004</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.15388156131588</v>
       </c>
       <c r="E21">
-        <v>-27.94704015306647</v>
+        <v>-27.63826162437946</v>
       </c>
       <c r="F21">
-        <v>-1.480235538699431</v>
+        <v>-2.687122941105963</v>
       </c>
       <c r="G21">
-        <v>-4.949068099146403</v>
+        <v>-4.699846920404528</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.474437270707686</v>
       </c>
       <c r="E22">
-        <v>-28.92122812396655</v>
+        <v>-28.60990006441322</v>
       </c>
       <c r="F22">
-        <v>-1.74289758824871</v>
+        <v>-2.446246125882908</v>
       </c>
       <c r="G22">
-        <v>-5.768788969579802</v>
+        <v>-5.220267989723498</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.749009210924485</v>
       </c>
       <c r="E23">
-        <v>-29.20006891098886</v>
+        <v>-28.26862973472118</v>
       </c>
       <c r="F23">
-        <v>-1.743997660159627</v>
+        <v>-2.445455863380638</v>
       </c>
       <c r="G23">
-        <v>-5.690583952305598</v>
+        <v>-4.362588404136815</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.958683576692354</v>
       </c>
       <c r="E24">
-        <v>-27.53971750149854</v>
+        <v>-27.59854690733219</v>
       </c>
       <c r="F24">
-        <v>-1.428726825225955</v>
+        <v>-2.187755734574128</v>
       </c>
       <c r="G24">
-        <v>-4.733008655071408</v>
+        <v>-4.392214476167753</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.080966033653821</v>
       </c>
       <c r="E25">
-        <v>-29.2585405673759</v>
+        <v>-28.08616393153012</v>
       </c>
       <c r="F25">
-        <v>-1.681711058408327</v>
+        <v>-1.949136220523702</v>
       </c>
       <c r="G25">
-        <v>-5.209386226535914</v>
+        <v>-3.758582681042326</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.096977527917941</v>
       </c>
       <c r="E26">
-        <v>-29.97157597072764</v>
+        <v>-28.90536035104368</v>
       </c>
       <c r="F26">
-        <v>-1.617649265312827</v>
+        <v>-1.825872665884928</v>
       </c>
       <c r="G26">
-        <v>-5.192780530110929</v>
+        <v>-4.961267459458616</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.994398039489788</v>
       </c>
       <c r="E27">
-        <v>-30.72097954883499</v>
+        <v>-29.14877035742997</v>
       </c>
       <c r="F27">
-        <v>-1.661275234581263</v>
+        <v>-1.875186205740985</v>
       </c>
       <c r="G27">
-        <v>-4.868108707983525</v>
+        <v>-4.544473086609913</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.764345770387177</v>
       </c>
       <c r="E28">
-        <v>-28.61137634693972</v>
+        <v>-28.54986155601953</v>
       </c>
       <c r="F28">
-        <v>-1.473732026220052</v>
+        <v>-2.09025523452982</v>
       </c>
       <c r="G28">
-        <v>-5.759198319152533</v>
+        <v>-4.527023201072415</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.409811942712504</v>
       </c>
       <c r="E29">
-        <v>-29.9007642226697</v>
+        <v>-28.55266468143028</v>
       </c>
       <c r="F29">
-        <v>-1.922859578139499</v>
+        <v>-2.013862364276247</v>
       </c>
       <c r="G29">
-        <v>-5.064890845383344</v>
+        <v>-4.799692973868947</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.9426436859178179</v>
       </c>
       <c r="E30">
-        <v>-31.32738750320212</v>
+        <v>-27.05083703305247</v>
       </c>
       <c r="F30">
-        <v>-1.25534704271781</v>
+        <v>-1.844283131412147</v>
       </c>
       <c r="G30">
-        <v>-6.728698201419179</v>
+        <v>-5.200103456843797</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.3816401991968225</v>
       </c>
       <c r="E31">
-        <v>-30.3723096926144</v>
+        <v>-27.28198393182599</v>
       </c>
       <c r="F31">
-        <v>-1.310235495194708</v>
+        <v>-1.938338451428211</v>
       </c>
       <c r="G31">
-        <v>-5.240985383708257</v>
+        <v>-4.465708587139574</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.2433714307721994</v>
       </c>
       <c r="E32">
-        <v>-29.87863357019421</v>
+        <v>-28.42820863027747</v>
       </c>
       <c r="F32">
-        <v>-1.893554424530661</v>
+        <v>-2.103444500317194</v>
       </c>
       <c r="G32">
-        <v>-4.56252218089002</v>
+        <v>-5.251668514163486</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.8992429321782887</v>
       </c>
       <c r="E33">
-        <v>-29.126943112713</v>
+        <v>-27.62832162393262</v>
       </c>
       <c r="F33">
-        <v>-0.8465518712732681</v>
+        <v>-2.674152364312928</v>
       </c>
       <c r="G33">
-        <v>-4.60926377335899</v>
+        <v>-4.902680735050135</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.550992616422488</v>
       </c>
       <c r="E34">
-        <v>-28.08617298847813</v>
+        <v>-25.83225184843243</v>
       </c>
       <c r="F34">
-        <v>-1.948728663761525</v>
+        <v>-1.972868118246506</v>
       </c>
       <c r="G34">
-        <v>-5.831722440281347</v>
+        <v>-5.135054547542658</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.162276610505826</v>
       </c>
       <c r="E35">
-        <v>-28.07184942519187</v>
+        <v>-26.2266728775525</v>
       </c>
       <c r="F35">
-        <v>-1.054496112030625</v>
+        <v>-2.078856070699897</v>
       </c>
       <c r="G35">
-        <v>-6.435943348835888</v>
+        <v>-5.329261080512923</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.702998218558111</v>
       </c>
       <c r="E36">
-        <v>-25.78792261637134</v>
+        <v>-26.37356751741331</v>
       </c>
       <c r="F36">
-        <v>-1.476179851895325</v>
+        <v>-1.612534924967943</v>
       </c>
       <c r="G36">
-        <v>-5.924520342292658</v>
+        <v>-6.090067482529452</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.148522397206713</v>
       </c>
       <c r="E37">
-        <v>-26.88106454250491</v>
+        <v>-25.22866060489806</v>
       </c>
       <c r="F37">
-        <v>-1.243338200479426</v>
+        <v>-1.906618606840212</v>
       </c>
       <c r="G37">
-        <v>-6.173542888302175</v>
+        <v>-6.110731907785583</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.48158909690239</v>
       </c>
       <c r="E38">
-        <v>-25.81222693637051</v>
+        <v>-25.98161903510143</v>
       </c>
       <c r="F38">
-        <v>-0.7374376602417116</v>
+        <v>-1.705819034932001</v>
       </c>
       <c r="G38">
-        <v>-7.525099589073951</v>
+        <v>-6.471313217377462</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.696380158219672</v>
       </c>
       <c r="E39">
-        <v>-25.67250087086384</v>
+        <v>-24.57358514037049</v>
       </c>
       <c r="F39">
-        <v>-1.52505187192569</v>
+        <v>-1.768322668942835</v>
       </c>
       <c r="G39">
-        <v>-6.576734229530014</v>
+        <v>-6.755361335192469</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.79610996196086</v>
       </c>
       <c r="E40">
-        <v>-26.26432713892628</v>
+        <v>-23.804025324455</v>
       </c>
       <c r="F40">
-        <v>-1.498101766843011</v>
+        <v>-2.023480538190153</v>
       </c>
       <c r="G40">
-        <v>-6.252224624134034</v>
+        <v>-6.447831517867411</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.791431098001815</v>
       </c>
       <c r="E41">
-        <v>-23.25439084872203</v>
+        <v>-22.9457753450993</v>
       </c>
       <c r="F41">
-        <v>-1.239474694912769</v>
+        <v>-1.950333211420748</v>
       </c>
       <c r="G41">
-        <v>-7.70666645917528</v>
+        <v>-6.341334578414596</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.701578271980929</v>
       </c>
       <c r="E42">
-        <v>-23.20407497402281</v>
+        <v>-23.46257385580265</v>
       </c>
       <c r="F42">
-        <v>-1.568069819520471</v>
+        <v>-1.73006452044454</v>
       </c>
       <c r="G42">
-        <v>-6.740536712267613</v>
+        <v>-5.973523037364949</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.549231603959769</v>
       </c>
       <c r="E43">
-        <v>-23.73597594554174</v>
+        <v>-22.507532273007</v>
       </c>
       <c r="F43">
-        <v>-2.187758219676336</v>
+        <v>-1.775182379405418</v>
       </c>
       <c r="G43">
-        <v>-7.184298789079219</v>
+        <v>-7.089815819388419</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.358631467971173</v>
       </c>
       <c r="E44">
-        <v>-23.76837717706662</v>
+        <v>-21.45082644873914</v>
       </c>
       <c r="F44">
-        <v>-1.193179725872513</v>
+        <v>-1.705029600797133</v>
       </c>
       <c r="G44">
-        <v>-7.5157042608335</v>
+        <v>-6.437777391064644</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.157544631439383</v>
       </c>
       <c r="E45">
-        <v>-22.80285670541722</v>
+        <v>-21.3494339157074</v>
       </c>
       <c r="F45">
-        <v>-0.6520826830572506</v>
+        <v>-1.559776205083642</v>
       </c>
       <c r="G45">
-        <v>-6.28494605624419</v>
+        <v>-6.852919801689252</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.966709967822491</v>
       </c>
       <c r="E46">
-        <v>-23.16751207488488</v>
+        <v>-20.47252662344009</v>
       </c>
       <c r="F46">
-        <v>-0.7686058121394458</v>
+        <v>-1.600940266430958</v>
       </c>
       <c r="G46">
-        <v>-6.789284495333381</v>
+        <v>-6.093616387347551</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.805159448523366</v>
       </c>
       <c r="E47">
-        <v>-21.07742659596267</v>
+        <v>-19.45547664605741</v>
       </c>
       <c r="F47">
-        <v>-0.644425254785772</v>
+        <v>-1.479405514561826</v>
       </c>
       <c r="G47">
-        <v>-6.305557512771693</v>
+        <v>-6.95304063043343</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.690045214128611</v>
       </c>
       <c r="E48">
-        <v>-20.82993643449548</v>
+        <v>-19.43778389810944</v>
       </c>
       <c r="F48">
-        <v>-0.9261190454143691</v>
+        <v>-1.663883763532679</v>
       </c>
       <c r="G48">
-        <v>-8.568232625225066</v>
+        <v>-7.569775401126416</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.625543122577765</v>
       </c>
       <c r="E49">
-        <v>-20.41635090337494</v>
+        <v>-18.35467707037687</v>
       </c>
       <c r="F49">
-        <v>-0.5640139742612184</v>
+        <v>-1.617921798188348</v>
       </c>
       <c r="G49">
-        <v>-6.482555830028827</v>
+        <v>-6.920070907407828</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.617926283371205</v>
       </c>
       <c r="E50">
-        <v>-17.49313941889159</v>
+        <v>-18.52398312810164</v>
       </c>
       <c r="F50">
-        <v>-0.8587272153596153</v>
+        <v>-1.632270778339641</v>
       </c>
       <c r="G50">
-        <v>-6.689862191697989</v>
+        <v>-7.453333582873631</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.667897718960775</v>
       </c>
       <c r="E51">
-        <v>-19.34941072784975</v>
+        <v>-17.98163949552101</v>
       </c>
       <c r="F51">
-        <v>-1.311506210790603</v>
+        <v>-1.891818994821796</v>
       </c>
       <c r="G51">
-        <v>-8.053989033882377</v>
+        <v>-7.85443265932065</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.764549849963677</v>
       </c>
       <c r="E52">
-        <v>-17.46419794150857</v>
+        <v>-17.58208317687624</v>
       </c>
       <c r="F52">
-        <v>-0.6140100888571824</v>
+        <v>-1.600951863574597</v>
       </c>
       <c r="G52">
-        <v>-7.942360748843692</v>
+        <v>-7.292907856586089</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.904261594237929</v>
       </c>
       <c r="E53">
-        <v>-18.57942976385155</v>
+        <v>-15.3315040506482</v>
       </c>
       <c r="F53">
-        <v>-0.8959598450132447</v>
+        <v>-1.64283991803196</v>
       </c>
       <c r="G53">
-        <v>-8.412944865614474</v>
+        <v>-7.039574980284439</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.075996133814342</v>
       </c>
       <c r="E54">
-        <v>-18.34919308835358</v>
+        <v>-16.72795410886751</v>
       </c>
       <c r="F54">
-        <v>-0.5540528562425543</v>
+        <v>-1.708860800035081</v>
       </c>
       <c r="G54">
-        <v>-7.979240226151173</v>
+        <v>-7.297456546157047</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.262883978144244</v>
       </c>
       <c r="E55">
-        <v>-16.95897421036882</v>
+        <v>-16.63466301583549</v>
       </c>
       <c r="F55">
-        <v>-0.8321573309148211</v>
+        <v>-1.891976384628328</v>
       </c>
       <c r="G55">
-        <v>-8.223475723310905</v>
+        <v>-8.762233904371898</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.458344283502197</v>
       </c>
       <c r="E56">
-        <v>-17.40441755613331</v>
+        <v>-15.46616275374028</v>
       </c>
       <c r="F56">
-        <v>-0.849456955754886</v>
+        <v>-1.857879125594295</v>
       </c>
       <c r="G56">
-        <v>-8.90830510520116</v>
+        <v>-8.259451421686165</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.649666680541532</v>
       </c>
       <c r="E57">
-        <v>-17.53386851411657</v>
+        <v>-15.44192636085123</v>
       </c>
       <c r="F57">
-        <v>-0.4471578414830977</v>
+        <v>-1.689851424875638</v>
       </c>
       <c r="G57">
-        <v>-9.297605397346217</v>
+        <v>-8.709483671749151</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.825252083845145</v>
       </c>
       <c r="E58">
-        <v>-15.23942206017623</v>
+        <v>-15.18561926049109</v>
       </c>
       <c r="F58">
-        <v>-1.110303223957228</v>
+        <v>-1.401210116839761</v>
       </c>
       <c r="G58">
-        <v>-9.095334375442286</v>
+        <v>-7.936938075250366</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.982895688952472</v>
       </c>
       <c r="E59">
-        <v>-15.65581071670751</v>
+        <v>-14.24868251677811</v>
       </c>
       <c r="F59">
-        <v>-0.8786270854770678</v>
+        <v>-1.767621041752664</v>
       </c>
       <c r="G59">
-        <v>-9.764521429659485</v>
+        <v>-9.060020786174881</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.115077978323067</v>
       </c>
       <c r="E60">
-        <v>-15.67694510490131</v>
+        <v>-13.35136992063223</v>
       </c>
       <c r="F60">
-        <v>-0.8511228026019158</v>
+        <v>-1.538362079353872</v>
       </c>
       <c r="G60">
-        <v>-9.72094140818052</v>
+        <v>-9.020674952440643</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.219504537603981</v>
       </c>
       <c r="E61">
-        <v>-14.61982266102475</v>
+        <v>-13.278026755604</v>
       </c>
       <c r="F61">
-        <v>-1.339196047963982</v>
+        <v>-1.576940806037051</v>
       </c>
       <c r="G61">
-        <v>-8.943992786114505</v>
+        <v>-9.259398391277488</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.299131268331188</v>
       </c>
       <c r="E62">
-        <v>-15.16771367426477</v>
+        <v>-12.07736527110631</v>
       </c>
       <c r="F62">
-        <v>-0.6676294824729917</v>
+        <v>-1.691764125208702</v>
       </c>
       <c r="G62">
-        <v>-8.99656424927813</v>
+        <v>-9.267499296212085</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.351533117965475</v>
       </c>
       <c r="E63">
-        <v>-15.05798422058491</v>
+        <v>-12.71182259347696</v>
       </c>
       <c r="F63">
-        <v>-1.379839894582339</v>
+        <v>-1.991503899707286</v>
       </c>
       <c r="G63">
-        <v>-9.027084168604672</v>
+        <v>-8.845593441050747</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.382002076638948</v>
       </c>
       <c r="E64">
-        <v>-14.86926006631524</v>
+        <v>-12.0134775598061</v>
       </c>
       <c r="F64">
-        <v>-0.9489687318531906</v>
+        <v>-2.106663536044473</v>
       </c>
       <c r="G64">
-        <v>-9.31421440431674</v>
+        <v>-9.006648170990751</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.395339878318799</v>
       </c>
       <c r="E65">
-        <v>-14.27716208981234</v>
+        <v>-12.72628653945746</v>
       </c>
       <c r="F65">
-        <v>-1.802940142705826</v>
+        <v>-1.757050245325539</v>
       </c>
       <c r="G65">
-        <v>-10.44201464263472</v>
+        <v>-9.495450219864141</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.38903049482262</v>
       </c>
       <c r="E66">
-        <v>-14.4919747828402</v>
+        <v>-13.45546595264655</v>
       </c>
       <c r="F66">
-        <v>-1.669903509448823</v>
+        <v>-2.026459347370619</v>
       </c>
       <c r="G66">
-        <v>-9.31389990249051</v>
+        <v>-8.864946890273325</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.368462772705876</v>
       </c>
       <c r="E67">
-        <v>-13.98935492425485</v>
+        <v>-11.56258645981038</v>
       </c>
       <c r="F67">
-        <v>-1.478849680034548</v>
+        <v>-2.31325836630267</v>
       </c>
       <c r="G67">
-        <v>-9.83241078703332</v>
+        <v>-8.991687815698784</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.333734637169317</v>
       </c>
       <c r="E68">
-        <v>-14.05073838942883</v>
+        <v>-11.53755305549598</v>
       </c>
       <c r="F68">
-        <v>-1.574418427295527</v>
+        <v>-2.260426750086923</v>
       </c>
       <c r="G68">
-        <v>-9.675550518291573</v>
+        <v>-9.208902640166984</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.279178027792346</v>
       </c>
       <c r="E69">
-        <v>-14.87011141942869</v>
+        <v>-12.64364641729149</v>
       </c>
       <c r="F69">
-        <v>-1.7997368459592</v>
+        <v>-1.808456241241068</v>
       </c>
       <c r="G69">
-        <v>-8.801973693025309</v>
+        <v>-8.944701242859908</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.206401707705917</v>
       </c>
       <c r="E70">
-        <v>-13.78350860976219</v>
+        <v>-12.03861964749669</v>
       </c>
       <c r="F70">
-        <v>-1.602049450383307</v>
+        <v>-2.300040107656198</v>
       </c>
       <c r="G70">
-        <v>-10.12479485851621</v>
+        <v>-9.353643001689459</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.110531118157755</v>
       </c>
       <c r="E71">
-        <v>-14.92988727632993</v>
+        <v>-12.47188592665456</v>
       </c>
       <c r="F71">
-        <v>-1.665547953644903</v>
+        <v>-2.388576844034812</v>
       </c>
       <c r="G71">
-        <v>-11.20338714793846</v>
+        <v>-8.692576715680094</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.984992590426185</v>
       </c>
       <c r="E72">
-        <v>-14.0111051849137</v>
+        <v>-11.89276655665764</v>
       </c>
       <c r="F72">
-        <v>-1.855044452341915</v>
+        <v>-2.818897970808502</v>
       </c>
       <c r="G72">
-        <v>-8.843984515918661</v>
+        <v>-8.348803045791094</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.830018942370394</v>
       </c>
       <c r="E73">
-        <v>-14.97388140131445</v>
+        <v>-11.3311678525964</v>
       </c>
       <c r="F73">
-        <v>-1.962920254106286</v>
+        <v>-2.846169482443468</v>
       </c>
       <c r="G73">
-        <v>-8.467870126656521</v>
+        <v>-8.354275377567509</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.640626658858194</v>
       </c>
       <c r="E74">
-        <v>-14.03070442041889</v>
+        <v>-12.89135847398506</v>
       </c>
       <c r="F74">
-        <v>-1.787296424303958</v>
+        <v>-2.900291695072776</v>
       </c>
       <c r="G74">
-        <v>-9.490567165193717</v>
+        <v>-7.991462760282163</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.414816476066931</v>
       </c>
       <c r="E75">
-        <v>-15.58549710079041</v>
+        <v>-12.35119303740213</v>
       </c>
       <c r="F75">
-        <v>-2.009028840480912</v>
+        <v>-3.036554819363683</v>
       </c>
       <c r="G75">
-        <v>-8.935769390994954</v>
+        <v>-8.014967633610988</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.154874029970782</v>
       </c>
       <c r="E76">
-        <v>-15.87630664461498</v>
+        <v>-12.96777194439049</v>
       </c>
       <c r="F76">
-        <v>-1.326224642803544</v>
+        <v>-2.681707075026459</v>
       </c>
       <c r="G76">
-        <v>-8.951898368862283</v>
+        <v>-8.505322328342297</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.860560612396279</v>
       </c>
       <c r="E77">
-        <v>-16.26837739572508</v>
+        <v>-14.18942743438774</v>
       </c>
       <c r="F77">
-        <v>-2.260966845633548</v>
+        <v>-3.085602453283442</v>
       </c>
       <c r="G77">
-        <v>-7.487829467392837</v>
+        <v>-8.064771480703783</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.536558308469549</v>
       </c>
       <c r="E78">
-        <v>-16.41476031802302</v>
+        <v>-14.08006025862849</v>
       </c>
       <c r="F78">
-        <v>-2.239913059723996</v>
+        <v>-3.158938647820685</v>
       </c>
       <c r="G78">
-        <v>-7.846785299124933</v>
+        <v>-6.952408316235429</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.189219432072997</v>
       </c>
       <c r="E79">
-        <v>-17.66113221915413</v>
+        <v>-15.80680815401927</v>
       </c>
       <c r="F79">
-        <v>-3.246846653340574</v>
+        <v>-3.221396721624365</v>
       </c>
       <c r="G79">
-        <v>-7.441289818201763</v>
+        <v>-7.384530514930958</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.823288554408435</v>
       </c>
       <c r="E80">
-        <v>-16.19792339711374</v>
+        <v>-16.09788034933629</v>
       </c>
       <c r="F80">
-        <v>-2.452169781180328</v>
+        <v>-3.377595335831046</v>
       </c>
       <c r="G80">
-        <v>-6.209660940135624</v>
+        <v>-7.415166303351374</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.447986468375256</v>
       </c>
       <c r="E81">
-        <v>-18.25765451476253</v>
+        <v>-15.56213017491083</v>
       </c>
       <c r="F81">
-        <v>-2.685645133659368</v>
+        <v>-3.099010408065155</v>
       </c>
       <c r="G81">
-        <v>-7.924891000032958</v>
+        <v>-6.981448421705916</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.0721418533497</v>
       </c>
       <c r="E82">
-        <v>-19.5170503071397</v>
+        <v>-16.63458603177736</v>
       </c>
       <c r="F82">
-        <v>-2.451178225399176</v>
+        <v>-2.927858105503138</v>
       </c>
       <c r="G82">
-        <v>-7.194223804605953</v>
+        <v>-6.477742296814727</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.7026729783261773</v>
       </c>
       <c r="E83">
-        <v>-19.17240173583793</v>
+        <v>-17.79051525002728</v>
       </c>
       <c r="F83">
-        <v>-2.632744762949189</v>
+        <v>-3.800339385971328</v>
       </c>
       <c r="G83">
-        <v>-7.206817119837341</v>
+        <v>-6.150504801894387</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.3505297809383106</v>
       </c>
       <c r="E84">
-        <v>-21.70445269248674</v>
+        <v>-18.84687691027056</v>
       </c>
       <c r="F84">
-        <v>-2.94016516000653</v>
+        <v>-3.66201362684745</v>
       </c>
       <c r="G84">
-        <v>-7.084115059969794</v>
+        <v>-5.821506096747156</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.02337482674128173</v>
       </c>
       <c r="E85">
-        <v>-21.06725111486744</v>
+        <v>-20.01530924525565</v>
       </c>
       <c r="F85">
-        <v>-2.930087242184071</v>
+        <v>-3.757478828183079</v>
       </c>
       <c r="G85">
-        <v>-5.807840164761044</v>
+        <v>-5.379227144337143</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.273017590708509</v>
       </c>
       <c r="E86">
-        <v>-22.22922131744359</v>
+        <v>-21.05590275900422</v>
       </c>
       <c r="F86">
-        <v>-2.987606589532261</v>
+        <v>-4.017750209407878</v>
       </c>
       <c r="G86">
-        <v>-6.225644253999225</v>
+        <v>-5.724526975719746</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.5295472393350787</v>
       </c>
       <c r="E87">
-        <v>-23.23797060197022</v>
+        <v>-21.18331137521002</v>
       </c>
       <c r="F87">
-        <v>-3.14899492551748</v>
+        <v>-4.374817978384606</v>
       </c>
       <c r="G87">
-        <v>-5.730423057325188</v>
+        <v>-5.572235259822193</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.7411231249702358</v>
       </c>
       <c r="E88">
-        <v>-25.3435117626806</v>
+        <v>-22.60808703834732</v>
       </c>
       <c r="F88">
-        <v>-3.63786257521883</v>
+        <v>-4.16879472163434</v>
       </c>
       <c r="G88">
-        <v>-6.102856119947657</v>
+        <v>-4.909675917774615</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.9027356236003423</v>
       </c>
       <c r="E89">
-        <v>-25.80819659450368</v>
+        <v>-23.58072174266277</v>
       </c>
       <c r="F89">
-        <v>-3.423027974404987</v>
+        <v>-4.435326903689498</v>
       </c>
       <c r="G89">
-        <v>-5.577512269411791</v>
+        <v>-5.329628551067782</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.007654125749954</v>
       </c>
       <c r="E90">
-        <v>-26.16844123028787</v>
+        <v>-26.3282193787005</v>
       </c>
       <c r="F90">
-        <v>-3.464236767592054</v>
+        <v>-4.612923904645295</v>
       </c>
       <c r="G90">
-        <v>-6.029911559535356</v>
+        <v>-4.811415615623506</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.053320103586173</v>
       </c>
       <c r="E91">
-        <v>-29.96517270848079</v>
+        <v>-26.8886723788378</v>
       </c>
       <c r="F91">
-        <v>-3.368561160936114</v>
+        <v>-5.00541597723534</v>
       </c>
       <c r="G91">
-        <v>-5.543698357273675</v>
+        <v>-5.275759354052761</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.035859375381681</v>
       </c>
       <c r="E92">
-        <v>-30.15285078525469</v>
+        <v>-28.4128118186514</v>
       </c>
       <c r="F92">
-        <v>-3.558074226981182</v>
+        <v>-5.199479265423986</v>
       </c>
       <c r="G92">
-        <v>-5.959539293007068</v>
+        <v>-5.089253150006841</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.9524284502734266</v>
       </c>
       <c r="E93">
-        <v>-31.95904622863603</v>
+        <v>-29.80894488369017</v>
       </c>
       <c r="F93">
-        <v>-4.583519346948121</v>
+        <v>-5.137063438357849</v>
       </c>
       <c r="G93">
-        <v>-6.096413798328236</v>
+        <v>-5.477417925031927</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.8054150821408329</v>
       </c>
       <c r="E94">
-        <v>-34.58431582273273</v>
+        <v>-31.88301994275826</v>
       </c>
       <c r="F94">
-        <v>-4.581817051935368</v>
+        <v>-5.49779590472456</v>
       </c>
       <c r="G94">
-        <v>-6.10075392353022</v>
+        <v>-5.19145631189522</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.5964441056606201</v>
       </c>
       <c r="E95">
-        <v>-36.10474191386003</v>
+        <v>-34.88874248789837</v>
       </c>
       <c r="F95">
-        <v>-4.710400382034921</v>
+        <v>-5.455582301877897</v>
       </c>
       <c r="G95">
-        <v>-5.268416564046658</v>
+        <v>-5.22711750844425</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3258396678908435</v>
       </c>
       <c r="E96">
-        <v>-37.6543109994637</v>
+        <v>-36.80236239168967</v>
       </c>
       <c r="F96">
-        <v>-4.334446664641768</v>
+        <v>-5.654029310362159</v>
       </c>
       <c r="G96">
-        <v>-6.981378900249592</v>
+        <v>-6.406797305908145</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.005616351573994169</v>
       </c>
       <c r="E97">
-        <v>-40.49149279898634</v>
+        <v>-38.51300476927216</v>
       </c>
       <c r="F97">
-        <v>-4.798183304076987</v>
+        <v>-5.754882213285596</v>
       </c>
       <c r="G97">
-        <v>-7.090242879762985</v>
+        <v>-6.463977048462437</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.3685564436008931</v>
       </c>
       <c r="E98">
-        <v>-44.12745439295895</v>
+        <v>-40.40981044907299</v>
       </c>
       <c r="F98">
-        <v>-5.470617998606111</v>
+        <v>-5.935617069963198</v>
       </c>
       <c r="G98">
-        <v>-7.072577808765434</v>
+        <v>-7.268982543973776</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.7729736497021689</v>
       </c>
       <c r="E99">
-        <v>-44.48005496461819</v>
+        <v>-41.41623436219668</v>
       </c>
       <c r="F99">
-        <v>-5.329537089500522</v>
+        <v>-6.317052094460674</v>
       </c>
       <c r="G99">
-        <v>-7.588811037977226</v>
+        <v>-6.805334020107767</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.221640270909645</v>
       </c>
       <c r="E100">
-        <v>-46.82413575791961</v>
+        <v>-44.50864774950262</v>
       </c>
       <c r="F100">
-        <v>-5.595534146213471</v>
+        <v>-6.968551873802547</v>
       </c>
       <c r="G100">
-        <v>-8.666532653922646</v>
+        <v>-8.405413374512632</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.667072568186998</v>
       </c>
       <c r="E101">
-        <v>-48.9364152879534</v>
+        <v>-45.98708130115681</v>
       </c>
       <c r="F101">
-        <v>-5.172351889717108</v>
+        <v>-6.696298572279956</v>
       </c>
       <c r="G101">
-        <v>-8.072885627820538</v>
+        <v>-8.682174981595702</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.162975971298186</v>
       </c>
       <c r="E102">
-        <v>-49.52595807299748</v>
+        <v>-48.15367081996459</v>
       </c>
       <c r="F102">
-        <v>-5.520625710345715</v>
+        <v>-6.712571021540549</v>
       </c>
       <c r="G102">
-        <v>-8.011246580424848</v>
+        <v>-8.587178877346316</v>
       </c>
     </row>
   </sheetData>
